--- a/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
+++ b/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비교표" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수직계열화지표" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수요예측지표" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +457,6 @@
           <t>수요예측 기반 SPA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -474,7 +474,6 @@
           <t>디자인~입고 2주 내외</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -492,7 +491,6 @@
           <t>정보시스템/물류 투자</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -510,7 +508,6 @@
           <t>소량 다품종+빠른 재보충</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -528,7 +525,6 @@
           <t>트렌드 예측 실패 리스크</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -713,4 +709,120 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20260725-tesla-zara-supply-chain-demand-forecast</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:46:17.211+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMMS 조교</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S09:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tesla의 생산·배터리·소프트웨어 통합과 Zara의 생산·유통 통제 및 협력 네트워크를 비교하고, 수요예측·리드타임·재고·시장 대응 속도 지표와 공개자료의 기준 시점·출처·비교 한계를 관련 산출물에 반영하기로 승인했다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tesla와 Zara의 수직계열화 기반 공급망 및 수요예측 방식 차이와 성과 영향을 비교한다.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tesla·Zara 케이스 스터디 문서; 케이스 스터디 분석 프레임</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/a79f54f3172beaecdbe161186ec9f2db84cac9c5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
+++ b/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,6 +822,56 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20260725-tesla-zara-deliverable-update</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-31T16:49:51.109Z</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IMMS 조교</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S09:B10000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>승인된 비교분석 프레임과 한계·출처 기준을 관련 산출물에 반영했으며, 산출물_설계서.docx·요구사항_추적표.xlsx·보고_장표.pptx는 deliverable_patch 기반 GitHub Actions 문서엔진으로 갱신 완료한 것으로 기록한다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tesla·Zara 케이스 스터디와 관련 설계·추적·보고 산출물에 공급망 수직계열화 및 수요예측 비교 분석을 반영하고 실행 결과를 기록한다.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tesla·Zara 케이스 스터디 문서; 케이스 스터디 분석 프레임; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>modify; modify; modify; modify; modify</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/8734ef539dea1dcc82d9b7b4a1bdc276592c00c7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
+++ b/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,6 +872,56 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20260725-tesla-zara-supply-chain-demand-forecast</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:53:22.187+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IMMS 조교</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S09:B01000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>공급망·수요예측 비교 범위, 지표 정의, 공개자료 기준, 분석 한계 및 cross-module 영향을 반영해 관련 산출물을 승인·갱신한다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tesla·Zara의 수직계열화·수요예측 비교, 5 Forces·VRIO, 단위경제 부록 및 분석 한계를 관련 산출물에 반영한다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tesla·Zara 케이스 스터디 문서; 케이스 스터디 분석 프레임; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>modify; modify; modify; modify; modify</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/c07baa4d0ab3b52c14e013730fce67b058f5f082</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
+++ b/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tesla의 생산·배터리·소프트웨어 통합과 Zara의 생산·유통 통제 및 협력 네트워크를 비교하고, 수요예측·리드타임·재고·시장 대응 속도 지표와 공개자료의 기준 시점·출처·비교 한계를 관련 산출물에 반영하기로 승인했다.</t>
+          <t>승인. 비교 지표의 정의·동등성 기준, 공개자료 출처·근거 수준, cross-module 영향 추적성, 경영진 메시지의 한계 고지 및 컴플라이언스 검토를 반영해 관련 산출물을 갱신한다.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -919,6 +919,56 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/c07baa4d0ab3b52c14e013730fce67b058f5f082</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20260725-tesla-zara-supply-chain-demand-forecast</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:57:08.822+09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IMMS 조교</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S09:B00100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>승인. 비교 지표의 정의·동등성 기준, 공개자료 출처·근거 수준, cross-module 영향 추적성, 경영진 메시지의 한계 고지 및 컴플라이언스 검토를 반영해 관련 산출물을 갱신한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tesla·Zara 케이스 스터디에 수직계열화·수요예측 비교 프레임과 근거·한계 기준을 반영하고 관련 산출물 간 추적성을 갱신한다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tesla·Zara 케이스 스터디 문서; 케이스 스터디 분석 프레임; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>modify; modify; modify; modify; modify</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/9d3d9f6d82715f93bde3b655c8c9e6a2a4b7291d</t>
         </is>
       </c>
     </row>

--- a/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
+++ b/scenarios/S09_kaist_case_study/deliverables/비교표_지표_시트.xlsx
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,6 +972,56 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20260725-tesla-zara-deliverable-approval</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-01T02:01:09.958+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IMMS 조교</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S09:B00010</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>승인된 변경을 deliverable_patch 기반으로 관련 산출물에 반영한 것으로 기록하되, 비교 지표 정의·기준 시점·공개자료 출처·근거 수준·추적 ID와 컴플라이언스 및 일반화 한계 고지를 유지한다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tesla·Zara 케이스 스터디에 수직계열화 기반 공급망 비교와 수요예측 차이 분석을 반영하고, 근거 수준·비교 한계·cross-module 추적성을 함께 갱신한다.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tesla·Zara 케이스 스터디 문서; 케이스 스터디 분석 프레임; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>modify; modify; modify; modify; modify</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/a0ec50f8e55f4f698d67205d91202b19082b53f7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
